--- a/template_relatorio_canais_eficiencia.xlsx
+++ b/template_relatorio_canais_eficiencia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://quantaprevi-my.sharepoint.com/personal/ac_kleber_quanta-previdencia_com_br/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="8_{B9F27261-3ACF-4341-8A48-9B8D9DABB3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA05208E-7C8C-438E-9845-F48495B52AEC}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="8_{B9F27261-3ACF-4341-8A48-9B8D9DABB3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A107148C-2474-442F-AA2A-6DAA9D53E057}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{93432986-D364-49ED-9430-64788DB7419B}"/>
+    <workbookView xWindow="2565" yWindow="2550" windowWidth="26250" windowHeight="11385" xr2:uid="{93432986-D364-49ED-9430-64788DB7419B}"/>
   </bookViews>
   <sheets>
     <sheet name="TEMPLATE" sheetId="1" r:id="rId1"/>
@@ -132,7 +132,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,12 +147,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -853,9 +847,7 @@
       <c r="F2" s="3">
         <v>7</v>
       </c>
-      <c r="G2" s="3">
-        <v>7</v>
-      </c>
+      <c r="G2" s="3"/>
       <c r="H2" s="3">
         <v>23</v>
       </c>
